--- a/campo.xlsx
+++ b/campo.xlsx
@@ -359,7 +359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,9 +642,133 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>46316.33081112269</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46316.33529424768</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46315</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ee.kobotoolbox.org:Uwhrmqi2VK0M3pFo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Flavio Henrique dos Santos</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BRO-2610210802</t>
+        </is>
+      </c>
+      <c r="H3" s="1">
+        <v>46316</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>rua do castelo</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Outro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-22.940962 -42.16247 0 0</t>
+        </is>
+      </c>
+      <c r="L3">
+        <v>-22.940962</v>
+      </c>
+      <c r="M3">
+        <v>-42.16247</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Alcantarea</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="S3">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>20260820_104517.jpg-8_2_43.jpeg</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>https://kf.kobotoolbox.org/api/v2/assets/aRYuJsgg5ZhZ66HouWjaes/data/898093267/attachments/attRbsFmiCuuHYj4JTJTQaAQ/</t>
+        </is>
+      </c>
+      <c r="W3">
+        <v>898093267</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
+        </is>
+      </c>
+      <c r="Y3" s="1">
+        <v>46316.46030092592</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>vB5KMx9aWRpLa9az5JUKiJ</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>uuid:9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
+        </is>
+      </c>
+      <c r="AE3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="U2" r:id="rId1"/>
+    <hyperlink ref="U3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -652,7 +776,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,6 +1132,250 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>uuid:d9fd4858-d703-4e11-a5cf-c382cbc7eb8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BRO-2610210802</t>
+        </is>
+      </c>
+      <c r="B5" s="1">
+        <v>46316</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nublado</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sombreada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SECA</t>
+        </is>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PESQUISA SOBRE BROMÉLIAS - ATIVIDADE DE CAMPO - v4</t>
+        </is>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>898093267</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
+        </is>
+      </c>
+      <c r="Q5" s="1">
+        <v>46316.46030092592</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>vB5KMx9aWRpLa9az5JUKiJ</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>uuid:9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BRO-2610210802</t>
+        </is>
+      </c>
+      <c r="B6" s="1">
+        <v>46316</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nublado</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sombreada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ÁGUA</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>80</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ausência</t>
+        </is>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PESQUISA SOBRE BROMÉLIAS - ATIVIDADE DE CAMPO - v4</t>
+        </is>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <v>898093267</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
+        </is>
+      </c>
+      <c r="Q6" s="1">
+        <v>46316.46030092592</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>vB5KMx9aWRpLa9az5JUKiJ</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>uuid:9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BRO-2610210802</t>
+        </is>
+      </c>
+      <c r="B7" s="1">
+        <v>46316</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nublado</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sombreada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ÁGUA</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>19</v>
+      </c>
+      <c r="I7">
+        <v>5.8</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PESQUISA SOBRE BROMÉLIAS - ATIVIDADE DE CAMPO - v4</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7">
+        <v>898093267</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
+        </is>
+      </c>
+      <c r="Q7" s="1">
+        <v>46316.46030092592</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>vB5KMx9aWRpLa9az5JUKiJ</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>uuid:9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,6 +1525,63 @@
       <c r="P2" t="inlineStr">
         <is>
           <t>uuid:d9fd4858-d703-4e11-a5cf-c382cbc7eb8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Larva</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BRO-2610210802-2</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>rep_visitas</t>
+        </is>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>898093267</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
+        </is>
+      </c>
+      <c r="K3" s="1">
+        <v>46316.46030092592</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>vB5KMx9aWRpLa9az5JUKiJ</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>uuid:9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
         </is>
       </c>
     </row>

--- a/campo.xlsx
+++ b/campo.xlsx
@@ -359,7 +359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,136 @@
       </c>
       <c r="AE3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>46316.39743648148</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46316.40042224537</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46315</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ee.kobotoolbox.org:Uwhrmqi2VK0M3pFo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Flavio Henrique dos Santos</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BRO-2610210936</t>
+        </is>
+      </c>
+      <c r="H4" s="1">
+        <v>46316</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>lagoa azul</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Outro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-22.942991 -42.1634 0 0</t>
+        </is>
+      </c>
+      <c r="L4">
+        <v>-22.942991</v>
+      </c>
+      <c r="M4">
+        <v>-42.1634</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Aechmea</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="S4">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>capa Albopictus1-9_34_27.png</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>https://kf.kobotoolbox.org/api/v2/assets/aRYuJsgg5ZhZ66HouWjaes/data/898169598/attachments/att3WcagMjtyWmCwjkRwbo4p/</t>
+        </is>
+      </c>
+      <c r="W4">
+        <v>898169598</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>d4573409-8ac7-4574-9bd3-87326429afc7</t>
+        </is>
+      </c>
+      <c r="Y4" s="1">
+        <v>46316.52542824074</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>vB5KMx9aWRpLa9az5JUKiJ</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>uuid:d4573409-8ac7-4574-9bd3-87326429afc7</t>
+        </is>
+      </c>
+      <c r="AE4">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="U2" r:id="rId1"/>
     <hyperlink ref="U3" r:id="rId2"/>
+    <hyperlink ref="U4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -776,7 +900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1376,6 +1500,164 @@
       <c r="V7" t="inlineStr">
         <is>
           <t>uuid:9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BRO-2610210936</t>
+        </is>
+      </c>
+      <c r="B8" s="1">
+        <v>46316</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sol</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ensolarada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SECA</t>
+        </is>
+      </c>
+      <c r="L8">
+        <v>7</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PESQUISA SOBRE BROMÉLIAS - ATIVIDADE DE CAMPO - v4</t>
+        </is>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8">
+        <v>898169598</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>d4573409-8ac7-4574-9bd3-87326429afc7</t>
+        </is>
+      </c>
+      <c r="Q8" s="1">
+        <v>46316.52542824074</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>vB5KMx9aWRpLa9az5JUKiJ</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>uuid:d4573409-8ac7-4574-9bd3-87326429afc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BRO-2610210936</t>
+        </is>
+      </c>
+      <c r="B9" s="1">
+        <v>46316</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sol</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ensolarada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ÁGUA</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>90</v>
+      </c>
+      <c r="H9">
+        <v>18</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Presença</t>
+        </is>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PESQUISA SOBRE BROMÉLIAS - ATIVIDADE DE CAMPO - v4</t>
+        </is>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9">
+        <v>898169598</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>d4573409-8ac7-4574-9bd3-87326429afc7</t>
+        </is>
+      </c>
+      <c r="Q9" s="1">
+        <v>46316.52542824074</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>vB5KMx9aWRpLa9az5JUKiJ</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>uuid:d4573409-8ac7-4574-9bd3-87326429afc7</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1668,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1582,6 +1864,63 @@
       <c r="P3" t="inlineStr">
         <is>
           <t>uuid:9f4bfb3d-8316-4c92-8b77-68b948119b49</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Larva</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BRO-2610210936-3</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>rep_visitas</t>
+        </is>
+      </c>
+      <c r="H4">
+        <v>8</v>
+      </c>
+      <c r="I4">
+        <v>898169598</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>d4573409-8ac7-4574-9bd3-87326429afc7</t>
+        </is>
+      </c>
+      <c r="K4" s="1">
+        <v>46316.52542824074</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>vB5KMx9aWRpLa9az5JUKiJ</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>uuid:d4573409-8ac7-4574-9bd3-87326429afc7</t>
         </is>
       </c>
     </row>
